--- a/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
+++ b/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_JabulanePoulo_2026\Projects\Timesheet\Jabulane_Poulo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9F838D-7DCB-4106-B849-CB8763AE3C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCBF873A-6E14-4CED-A777-18CDD3C75C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <sheet name="Key" sheetId="2" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Apr!$A$1:$J$142</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Apr!$A$1:$J$141</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="261">
   <si>
     <t>Date</t>
   </si>
@@ -827,9 +827,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sales Analysis Presentation </t>
-  </si>
-  <si>
-    <t>Data Migration Project</t>
   </si>
 </sst>
 </file>
@@ -3543,7 +3540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B63D3D5-6C83-45F2-B2A7-43EE15BF1EF3}">
-  <dimension ref="A3:J142"/>
+  <dimension ref="A3:J141"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
@@ -3576,7 +3573,7 @@
         <v>93</v>
       </c>
       <c r="B6" s="72">
-        <f>F137</f>
+        <f>F136</f>
         <v>0</v>
       </c>
       <c r="C6" s="37"/>
@@ -3634,30 +3631,28 @@
       <c r="C9" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D9" s="27"/>
       <c r="E9" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H9" s="29">
-        <f>J9-I9</f>
-        <v>1.1805555555555569E-2</v>
+        <f t="shared" ref="H9:H13" si="0">J9-I9</f>
+        <v>0.11319444444444443</v>
       </c>
       <c r="I9" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.34513888888888888</v>
       </c>
       <c r="J9" s="30">
-        <v>0.34513888888888888</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46113</v>
       </c>
@@ -3667,30 +3662,28 @@
       <c r="C10" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D10" s="27"/>
       <c r="E10" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F10" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H10" s="29">
-        <f t="shared" ref="H10:H14" si="0">J10-I10</f>
-        <v>0.11319444444444443</v>
+        <f t="shared" si="0"/>
+        <v>2.5000000000000022E-2</v>
       </c>
       <c r="I10" s="30">
-        <v>0.34513888888888888</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J10" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.48333333333333334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46113</v>
       </c>
@@ -3700,27 +3693,25 @@
       <c r="C11" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D11" s="27"/>
       <c r="E11" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H11" s="29">
         <f t="shared" si="0"/>
-        <v>2.5000000000000022E-2</v>
+        <v>2.0138888888888873E-2</v>
       </c>
       <c r="I11" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.48333333333333334</v>
       </c>
       <c r="J11" s="30">
-        <v>0.48333333333333334</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -3733,9 +3724,7 @@
       <c r="C12" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D12" s="27"/>
       <c r="E12" s="27" t="s">
         <v>33</v>
       </c>
@@ -3747,16 +3736,16 @@
       </c>
       <c r="H12" s="29">
         <f t="shared" si="0"/>
-        <v>2.0138888888888873E-2</v>
+        <v>0.12847222222222221</v>
       </c>
       <c r="I12" s="30">
-        <v>0.48333333333333334</v>
+        <v>0.53819444444444442</v>
       </c>
       <c r="J12" s="30">
-        <v>0.50347222222222221</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46113</v>
       </c>
@@ -3766,42 +3755,38 @@
       <c r="C13" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D13" s="27"/>
       <c r="E13" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H13" s="29">
         <f t="shared" si="0"/>
-        <v>0.12847222222222221</v>
+        <v>7.9166666666666718E-2</v>
       </c>
       <c r="I13" s="30">
-        <v>0.53819444444444442</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J13" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.74583333333333335</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D14" s="27"/>
       <c r="E14" s="27" t="s">
         <v>62</v>
       </c>
@@ -3809,17 +3794,17 @@
         <v>15</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H14" s="29">
-        <f t="shared" si="0"/>
-        <v>7.9166666666666718E-2</v>
+        <f t="shared" ref="H14:H131" si="1">J14-I14</f>
+        <v>6.9444444444444753E-3</v>
       </c>
       <c r="I14" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J14" s="30">
-        <v>0.74583333333333335</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -3832,30 +3817,28 @@
       <c r="C15" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D15" s="27"/>
       <c r="E15" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H15" s="29">
-        <f t="shared" ref="H15:H132" si="1">J15-I15</f>
-        <v>6.9444444444444753E-3</v>
+        <f t="shared" si="1"/>
+        <v>0.11805555555555552</v>
       </c>
       <c r="I15" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.34027777777777779</v>
       </c>
       <c r="J15" s="30">
-        <v>0.34027777777777779</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46114</v>
       </c>
@@ -3865,30 +3848,28 @@
       <c r="C16" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D16" s="27"/>
       <c r="E16" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F16" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H16" s="29">
         <f t="shared" si="1"/>
-        <v>0.11805555555555552</v>
+        <v>3.5416666666666707E-2</v>
       </c>
       <c r="I16" s="30">
-        <v>0.34027777777777779</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J16" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.49375000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46114</v>
       </c>
@@ -3898,27 +3879,25 @@
       <c r="C17" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D17" s="27"/>
       <c r="E17" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H17" s="29">
         <f t="shared" si="1"/>
-        <v>3.5416666666666707E-2</v>
+        <v>2.8472222222222232E-2</v>
       </c>
       <c r="I17" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.49375000000000002</v>
       </c>
       <c r="J17" s="30">
-        <v>0.49375000000000002</v>
+        <v>0.52222222222222225</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -3931,9 +3910,7 @@
       <c r="C18" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D18" s="27"/>
       <c r="E18" s="27" t="s">
         <v>33</v>
       </c>
@@ -3945,13 +3922,13 @@
       </c>
       <c r="H18" s="29">
         <f t="shared" si="1"/>
-        <v>2.8472222222222232E-2</v>
+        <v>0.10555555555555551</v>
       </c>
       <c r="I18" s="30">
-        <v>0.49375000000000002</v>
+        <v>0.56111111111111112</v>
       </c>
       <c r="J18" s="30">
-        <v>0.52222222222222225</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -3964,99 +3941,83 @@
       <c r="C19" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D19" s="27"/>
       <c r="E19" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H19" s="29">
         <f t="shared" si="1"/>
-        <v>0.10555555555555551</v>
+        <v>4.9305555555555602E-2</v>
       </c>
       <c r="I19" s="30">
-        <v>0.56111111111111112</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J19" s="30">
+        <v>0.71597222222222223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="47">
+        <v>46115</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="50">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I20" s="51">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J20" s="51">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
-      <c r="A20" s="22">
-        <v>46114</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="H20" s="29">
-        <f t="shared" si="1"/>
-        <v>4.9305555555555602E-2</v>
-      </c>
-      <c r="I20" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J20" s="30">
-        <v>0.71597222222222223</v>
-      </c>
-    </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="47">
-        <v>46115</v>
-      </c>
-      <c r="B21" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="H21" s="50">
-        <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="I21" s="51">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J21" s="51">
-        <v>0.66666666666666663</v>
-      </c>
+      <c r="A21" s="31">
+        <v>46116</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="34">
+        <f t="shared" ref="H21" si="2">J21-I21</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="31">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
@@ -4064,60 +4025,72 @@
       <c r="F22" s="32"/>
       <c r="G22" s="33"/>
       <c r="H22" s="34">
-        <f t="shared" ref="H22" si="2">J22-I22</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="31">
-        <v>46117</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="47">
+      <c r="A23" s="47">
         <v>46118</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B23" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C23" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48" t="s">
+      <c r="D23" s="48"/>
+      <c r="E23" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="48" t="s">
+      <c r="F23" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="49" t="s">
+      <c r="G23" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="H24" s="50">
-        <f t="shared" ref="H24" si="3">J24-I24</f>
+      <c r="H23" s="50">
+        <f t="shared" ref="H23" si="3">J23-I23</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="I24" s="51">
+      <c r="I23" s="51">
         <v>0.33333333333333331</v>
       </c>
-      <c r="J24" s="51">
+      <c r="J23" s="51">
         <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+      <c r="A24" s="22">
+        <v>46119</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="H24" s="29">
+        <f t="shared" si="1"/>
+        <v>6.9444444444444753E-3</v>
+      </c>
+      <c r="I24" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J24" s="30">
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4130,30 +4103,28 @@
       <c r="C25" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D25" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D25" s="27"/>
       <c r="E25" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F25" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H25" s="29">
         <f t="shared" si="1"/>
-        <v>6.9444444444444753E-3</v>
+        <v>0.11805555555555552</v>
       </c>
       <c r="I25" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.34027777777777779</v>
       </c>
       <c r="J25" s="30">
-        <v>0.34027777777777779</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46119</v>
       </c>
@@ -4163,30 +4134,28 @@
       <c r="C26" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D26" s="27"/>
       <c r="E26" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F26" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H26" s="29">
         <f t="shared" si="1"/>
-        <v>0.11805555555555552</v>
+        <v>2.7083333333333348E-2</v>
       </c>
       <c r="I26" s="30">
-        <v>0.34027777777777779</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J26" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.48541666666666666</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46119</v>
       </c>
@@ -4196,9 +4165,7 @@
       <c r="C27" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D27" s="27"/>
       <c r="E27" s="27" t="s">
         <v>62</v>
       </c>
@@ -4206,17 +4173,17 @@
         <v>15</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H27" s="29">
         <f t="shared" si="1"/>
-        <v>2.7083333333333348E-2</v>
+        <v>1.8055555555555547E-2</v>
       </c>
       <c r="I27" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.48541666666666666</v>
       </c>
       <c r="J27" s="30">
-        <v>0.48541666666666666</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4229,30 +4196,28 @@
       <c r="C28" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D28" s="27"/>
       <c r="E28" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F28" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H28" s="29">
         <f t="shared" si="1"/>
-        <v>1.8055555555555547E-2</v>
+        <v>0.12847222222222221</v>
       </c>
       <c r="I28" s="30">
-        <v>0.48541666666666666</v>
+        <v>0.53819444444444442</v>
       </c>
       <c r="J28" s="30">
-        <v>0.50347222222222221</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46119</v>
       </c>
@@ -4262,42 +4227,38 @@
       <c r="C29" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D29" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D29" s="27"/>
       <c r="E29" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F29" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H29" s="29">
         <f t="shared" si="1"/>
-        <v>0.12847222222222221</v>
+        <v>5.7638888888888906E-2</v>
       </c>
       <c r="I29" s="30">
-        <v>0.53819444444444442</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J29" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.72430555555555554</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D30" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D30" s="27"/>
       <c r="E30" s="27" t="s">
         <v>62</v>
       </c>
@@ -4305,17 +4266,17 @@
         <v>15</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H30" s="29">
         <f t="shared" si="1"/>
-        <v>5.7638888888888906E-2</v>
+        <v>7.6388888888889173E-3</v>
       </c>
       <c r="I30" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J30" s="30">
-        <v>0.72430555555555554</v>
+        <v>0.34097222222222223</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4328,30 +4289,28 @@
       <c r="C31" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D31" s="27"/>
       <c r="E31" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F31" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H31" s="29">
         <f t="shared" si="1"/>
-        <v>7.6388888888889173E-3</v>
+        <v>0.11736111111111108</v>
       </c>
       <c r="I31" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.34097222222222223</v>
       </c>
       <c r="J31" s="30">
-        <v>0.34097222222222223</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46120</v>
       </c>
@@ -4361,30 +4320,28 @@
       <c r="C32" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D32" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D32" s="27"/>
       <c r="E32" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F32" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H32" s="29">
         <f t="shared" si="1"/>
-        <v>0.11736111111111108</v>
+        <v>3.2638888888888884E-2</v>
       </c>
       <c r="I32" s="30">
-        <v>0.34097222222222223</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J32" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.4909722222222222</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46120</v>
       </c>
@@ -4394,27 +4351,25 @@
       <c r="C33" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D33" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D33" s="27"/>
       <c r="E33" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F33" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G33" s="28" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H33" s="29">
         <f t="shared" si="1"/>
-        <v>3.2638888888888884E-2</v>
+        <v>1.5972222222222221E-2</v>
       </c>
       <c r="I33" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.4909722222222222</v>
       </c>
       <c r="J33" s="30">
-        <v>0.4909722222222222</v>
+        <v>0.50694444444444442</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4427,9 +4382,7 @@
       <c r="C34" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D34" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D34" s="27"/>
       <c r="E34" s="27" t="s">
         <v>33</v>
       </c>
@@ -4437,20 +4390,20 @@
         <v>15</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H34" s="29">
         <f t="shared" si="1"/>
-        <v>1.5972222222222221E-2</v>
+        <v>0.11805555555555547</v>
       </c>
       <c r="I34" s="30">
-        <v>0.4909722222222222</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="J34" s="30">
-        <v>0.50694444444444442</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46120</v>
       </c>
@@ -4460,30 +4413,28 @@
       <c r="C35" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D35" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D35" s="27"/>
       <c r="E35" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F35" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H35" s="29">
         <f t="shared" si="1"/>
-        <v>0.11805555555555547</v>
+        <v>2.2222222222222254E-2</v>
       </c>
       <c r="I35" s="30">
-        <v>0.54861111111111116</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J35" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.68888888888888888</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46120</v>
       </c>
@@ -4493,60 +4444,56 @@
       <c r="C36" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D36" s="27"/>
       <c r="E36" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F36" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H36" s="29">
         <f t="shared" si="1"/>
-        <v>2.2222222222222254E-2</v>
+        <v>2.9861111111111116E-2</v>
       </c>
       <c r="I36" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.68888888888888888</v>
       </c>
       <c r="J36" s="30">
-        <v>0.68888888888888888</v>
+        <v>0.71875</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C37" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D37" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D37" s="27"/>
       <c r="E37" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F37" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H37" s="29">
         <f t="shared" si="1"/>
-        <v>2.9861111111111116E-2</v>
+        <v>4.1666666666667074E-3</v>
       </c>
       <c r="I37" s="30">
-        <v>0.68888888888888888</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J37" s="30">
-        <v>0.71875</v>
+        <v>0.33750000000000002</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4559,30 +4506,28 @@
       <c r="C38" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D38" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D38" s="27"/>
       <c r="E38" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F38" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="H38" s="29">
         <f t="shared" si="1"/>
-        <v>4.1666666666667074E-3</v>
+        <v>0.12083333333333329</v>
       </c>
       <c r="I38" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.33750000000000002</v>
       </c>
       <c r="J38" s="30">
-        <v>0.33750000000000002</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A39" s="22">
         <v>46121</v>
       </c>
@@ -4592,30 +4537,28 @@
       <c r="C39" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D39" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D39" s="27"/>
       <c r="E39" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F39" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H39" s="29">
         <f t="shared" si="1"/>
-        <v>0.12083333333333329</v>
+        <v>3.6805555555555591E-2</v>
       </c>
       <c r="I39" s="30">
-        <v>0.33750000000000002</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J39" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.49513888888888891</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A40" s="22">
         <v>46121</v>
       </c>
@@ -4625,30 +4568,28 @@
       <c r="C40" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D40" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D40" s="27"/>
       <c r="E40" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F40" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G40" s="28" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H40" s="29">
         <f t="shared" si="1"/>
-        <v>3.6805555555555591E-2</v>
+        <v>0.125</v>
       </c>
       <c r="I40" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J40" s="30">
-        <v>0.49513888888888891</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A41" s="22">
         <v>46121</v>
       </c>
@@ -4658,9 +4599,7 @@
       <c r="C41" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D41" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D41" s="27"/>
       <c r="E41" s="27" t="s">
         <v>33</v>
       </c>
@@ -4668,50 +4607,48 @@
         <v>15</v>
       </c>
       <c r="G41" s="28" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H41" s="29">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>5.208333333333337E-2</v>
       </c>
       <c r="I41" s="30">
-        <v>0.54166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J41" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A42" s="22">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C42" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D42" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D42" s="27"/>
       <c r="E42" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F42" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G42" s="28" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H42" s="29">
         <f t="shared" si="1"/>
-        <v>5.208333333333337E-2</v>
+        <v>4.8611111111111494E-3</v>
       </c>
       <c r="I42" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J42" s="30">
-        <v>0.71875</v>
+        <v>0.33819444444444446</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4724,27 +4661,25 @@
       <c r="C43" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D43" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D43" s="27"/>
       <c r="E43" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F43" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G43" s="28" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H43" s="29">
         <f t="shared" si="1"/>
-        <v>4.8611111111111494E-3</v>
+        <v>0.12013888888888885</v>
       </c>
       <c r="I43" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.33819444444444446</v>
       </c>
       <c r="J43" s="30">
-        <v>0.33819444444444446</v>
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4757,27 +4692,25 @@
       <c r="C44" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D44" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D44" s="27"/>
       <c r="E44" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F44" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G44" s="28" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H44" s="29">
         <f t="shared" si="1"/>
-        <v>0.12013888888888885</v>
+        <v>3.2638888888888884E-2</v>
       </c>
       <c r="I44" s="30">
-        <v>0.33819444444444446</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J44" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.4909722222222222</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4790,68 +4723,52 @@
       <c r="C45" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D45" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D45" s="27"/>
       <c r="E45" s="27" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F45" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G45" s="28" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H45" s="29">
         <f t="shared" si="1"/>
-        <v>3.2638888888888884E-2</v>
+        <v>0.22847222222222224</v>
       </c>
       <c r="I45" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.4909722222222222</v>
       </c>
       <c r="J45" s="30">
-        <v>0.4909722222222222</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
-      <c r="A46" s="22">
-        <v>46122</v>
-      </c>
-      <c r="B46" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D46" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="E46" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="F46" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="H46" s="29">
-        <f t="shared" si="1"/>
-        <v>0.22847222222222224</v>
-      </c>
-      <c r="I46" s="30">
-        <v>0.4909722222222222</v>
-      </c>
-      <c r="J46" s="30">
         <v>0.71944444444444444</v>
       </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" s="31">
+        <v>46123</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="31">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C47" s="32"/>
       <c r="D47" s="32"/>
@@ -4865,24 +4782,36 @@
       <c r="I47" s="35"/>
       <c r="J47" s="35"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A48" s="31">
-        <v>46124</v>
-      </c>
-      <c r="B48" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="35"/>
-      <c r="J48" s="35"/>
+    <row r="48" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+      <c r="A48" s="22">
+        <v>46125</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F48" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="H48" s="29">
+        <f t="shared" si="1"/>
+        <v>7.6388888888889173E-3</v>
+      </c>
+      <c r="I48" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J48" s="30">
+        <v>0.34097222222222223</v>
+      </c>
     </row>
     <row r="49" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A49" s="22">
@@ -4894,27 +4823,25 @@
       <c r="C49" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D49" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D49" s="27"/>
       <c r="E49" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F49" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G49" s="28" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="H49" s="29">
         <f t="shared" si="1"/>
-        <v>7.6388888888889173E-3</v>
+        <v>0.11736111111111108</v>
       </c>
       <c r="I49" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.34097222222222223</v>
       </c>
       <c r="J49" s="30">
-        <v>0.34097222222222223</v>
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4927,27 +4854,25 @@
       <c r="C50" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D50" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D50" s="27"/>
       <c r="E50" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F50" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G50" s="28" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="H50" s="29">
         <f t="shared" si="1"/>
-        <v>0.11736111111111108</v>
+        <v>2.2222222222222254E-2</v>
       </c>
       <c r="I50" s="30">
-        <v>0.34097222222222223</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J50" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.48055555555555557</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4960,27 +4885,25 @@
       <c r="C51" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D51" s="27"/>
       <c r="E51" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F51" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G51" s="28" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H51" s="29">
         <f t="shared" si="1"/>
-        <v>2.2222222222222254E-2</v>
+        <v>2.6388888888888851E-2</v>
       </c>
       <c r="I51" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.48055555555555557</v>
       </c>
       <c r="J51" s="30">
-        <v>0.48055555555555557</v>
+        <v>0.50694444444444442</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -4993,9 +4916,7 @@
       <c r="C52" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D52" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D52" s="27"/>
       <c r="E52" s="27" t="s">
         <v>33</v>
       </c>
@@ -5003,20 +4924,20 @@
         <v>15</v>
       </c>
       <c r="G52" s="28" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H52" s="29">
         <f t="shared" si="1"/>
-        <v>2.6388888888888851E-2</v>
+        <v>0.11805555555555547</v>
       </c>
       <c r="I52" s="30">
-        <v>0.48055555555555557</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="J52" s="30">
-        <v>0.50694444444444442</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A53" s="22">
         <v>46125</v>
       </c>
@@ -5026,9 +4947,7 @@
       <c r="C53" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D53" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D53" s="27"/>
       <c r="E53" s="27" t="s">
         <v>33</v>
       </c>
@@ -5036,50 +4955,48 @@
         <v>15</v>
       </c>
       <c r="G53" s="28" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H53" s="29">
         <f t="shared" si="1"/>
-        <v>0.11805555555555547</v>
+        <v>4.3055555555555625E-2</v>
       </c>
       <c r="I53" s="30">
-        <v>0.54861111111111116</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J53" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.70972222222222225</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A54" s="22">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C54" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D54" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D54" s="27"/>
       <c r="E54" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F54" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G54" s="28" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H54" s="29">
         <f t="shared" si="1"/>
-        <v>4.3055555555555625E-2</v>
+        <v>5.5555555555555913E-3</v>
       </c>
       <c r="I54" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J54" s="30">
-        <v>0.70972222222222225</v>
+        <v>0.33888888888888891</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5092,27 +5009,25 @@
       <c r="C55" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D55" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D55" s="27"/>
       <c r="E55" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F55" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G55" s="28" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="H55" s="29">
         <f t="shared" si="1"/>
-        <v>5.5555555555555913E-3</v>
+        <v>0.11944444444444441</v>
       </c>
       <c r="I55" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.33888888888888891</v>
       </c>
       <c r="J55" s="30">
-        <v>0.33888888888888891</v>
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5125,27 +5040,25 @@
       <c r="C56" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D56" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D56" s="27"/>
       <c r="E56" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F56" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G56" s="28" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H56" s="29">
         <f t="shared" si="1"/>
-        <v>0.11944444444444441</v>
+        <v>2.8472222222222232E-2</v>
       </c>
       <c r="I56" s="30">
-        <v>0.33888888888888891</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J56" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.48680555555555555</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5158,27 +5071,25 @@
       <c r="C57" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D57" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D57" s="27"/>
       <c r="E57" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F57" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G57" s="28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H57" s="29">
         <f t="shared" si="1"/>
-        <v>2.8472222222222232E-2</v>
+        <v>3.8194444444444475E-2</v>
       </c>
       <c r="I57" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.48680555555555555</v>
       </c>
       <c r="J57" s="30">
-        <v>0.48680555555555555</v>
+        <v>0.52500000000000002</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5191,9 +5102,7 @@
       <c r="C58" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D58" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D58" s="27"/>
       <c r="E58" s="27" t="s">
         <v>33</v>
       </c>
@@ -5204,17 +5113,17 @@
         <v>239</v>
       </c>
       <c r="H58" s="29">
-        <f t="shared" si="1"/>
-        <v>3.8194444444444475E-2</v>
-      </c>
-      <c r="I58" s="30">
-        <v>0.48680555555555555</v>
+        <f>J58-I57</f>
+        <v>0.17986111111111108</v>
+      </c>
+      <c r="I58" s="122">
+        <v>0.56666666666666665</v>
       </c>
       <c r="J58" s="30">
-        <v>0.52500000000000002</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A59" s="22">
         <v>46126</v>
       </c>
@@ -5224,42 +5133,38 @@
       <c r="C59" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D59" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D59" s="27"/>
       <c r="E59" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F59" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H59" s="29">
-        <f>J59-I58</f>
-        <v>0.17986111111111108</v>
-      </c>
-      <c r="I59" s="122">
-        <v>0.56666666666666665</v>
+        <f t="shared" si="1"/>
+        <v>4.5138888888888951E-2</v>
+      </c>
+      <c r="I59" s="30">
+        <v>0.66666666666666663</v>
       </c>
       <c r="J59" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.71180555555555558</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A60" s="22">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C60" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D60" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D60" s="27"/>
       <c r="E60" s="27" t="s">
         <v>62</v>
       </c>
@@ -5267,17 +5172,17 @@
         <v>15</v>
       </c>
       <c r="G60" s="28" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H60" s="29">
         <f t="shared" si="1"/>
-        <v>4.5138888888888951E-2</v>
+        <v>2.7777777777778234E-3</v>
       </c>
       <c r="I60" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J60" s="30">
-        <v>0.71180555555555558</v>
+        <v>0.33611111111111114</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5290,30 +5195,28 @@
       <c r="C61" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D61" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D61" s="27"/>
       <c r="E61" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F61" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G61" s="28" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H61" s="29">
         <f t="shared" si="1"/>
-        <v>2.7777777777778234E-3</v>
+        <v>0.12222222222222218</v>
       </c>
       <c r="I61" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.33611111111111114</v>
       </c>
       <c r="J61" s="30">
-        <v>0.33611111111111114</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A62" s="22">
         <v>46127</v>
       </c>
@@ -5323,30 +5226,28 @@
       <c r="C62" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D62" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D62" s="27"/>
       <c r="E62" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F62" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G62" s="28" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H62" s="29">
         <f t="shared" si="1"/>
-        <v>0.12222222222222218</v>
+        <v>2.083333333333337E-2</v>
       </c>
       <c r="I62" s="30">
-        <v>0.33611111111111114</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J62" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A63" s="22">
         <v>46127</v>
       </c>
@@ -5356,27 +5257,25 @@
       <c r="C63" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D63" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D63" s="27"/>
       <c r="E63" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F63" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G63" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H63" s="29">
         <f t="shared" si="1"/>
-        <v>2.083333333333337E-2</v>
+        <v>2.0833333333333315E-2</v>
       </c>
       <c r="I63" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="J63" s="30">
-        <v>0.47916666666666669</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5389,9 +5288,7 @@
       <c r="C64" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D64" s="27"/>
       <c r="E64" s="27" t="s">
         <v>33</v>
       </c>
@@ -5403,16 +5300,16 @@
       </c>
       <c r="H64" s="29">
         <f t="shared" si="1"/>
-        <v>2.0833333333333315E-2</v>
+        <v>0.125</v>
       </c>
       <c r="I64" s="30">
-        <v>0.47916666666666669</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J64" s="30">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A65" s="22">
         <v>46127</v>
       </c>
@@ -5422,42 +5319,38 @@
       <c r="C65" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D65" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D65" s="27"/>
       <c r="E65" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F65" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G65" s="28" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H65" s="29">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>7.986111111111116E-2</v>
       </c>
       <c r="I65" s="30">
-        <v>0.54166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J65" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.74652777777777779</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A66" s="22">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C66" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D66" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D66" s="27"/>
       <c r="E66" s="27" t="s">
         <v>62</v>
       </c>
@@ -5465,17 +5358,17 @@
         <v>15</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H66" s="29">
         <f t="shared" si="1"/>
-        <v>7.986111111111116E-2</v>
+        <v>4.8611111111111494E-3</v>
       </c>
       <c r="I66" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J66" s="30">
-        <v>0.74652777777777779</v>
+        <v>0.33819444444444446</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5488,30 +5381,28 @@
       <c r="C67" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D67" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D67" s="27"/>
       <c r="E67" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F67" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G67" s="28" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="H67" s="29">
         <f t="shared" si="1"/>
-        <v>4.8611111111111494E-3</v>
+        <v>0.12013888888888885</v>
       </c>
       <c r="I67" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.33819444444444446</v>
       </c>
       <c r="J67" s="30">
-        <v>0.33819444444444446</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
         <v>46128</v>
       </c>
@@ -5521,30 +5412,28 @@
       <c r="C68" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D68" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D68" s="27"/>
       <c r="E68" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F68" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G68" s="28" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H68" s="29">
         <f t="shared" si="1"/>
-        <v>0.12013888888888885</v>
+        <v>2.6388888888888906E-2</v>
       </c>
       <c r="I68" s="30">
-        <v>0.33819444444444446</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J68" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.48472222222222222</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
         <v>46128</v>
       </c>
@@ -5554,27 +5443,25 @@
       <c r="C69" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D69" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D69" s="27"/>
       <c r="E69" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F69" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G69" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H69" s="29">
         <f t="shared" si="1"/>
-        <v>2.6388888888888906E-2</v>
+        <v>1.5277777777777779E-2</v>
       </c>
       <c r="I69" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.48472222222222222</v>
       </c>
       <c r="J69" s="30">
-        <v>0.48472222222222222</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5587,9 +5474,7 @@
       <c r="C70" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D70" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D70" s="27"/>
       <c r="E70" s="27" t="s">
         <v>33</v>
       </c>
@@ -5601,16 +5486,16 @@
       </c>
       <c r="H70" s="29">
         <f t="shared" si="1"/>
-        <v>1.5277777777777779E-2</v>
+        <v>0.125</v>
       </c>
       <c r="I70" s="30">
-        <v>0.48472222222222222</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J70" s="30">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
         <v>46128</v>
       </c>
@@ -5620,42 +5505,38 @@
       <c r="C71" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D71" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D71" s="27"/>
       <c r="E71" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F71" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G71" s="28" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H71" s="29">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>6.7361111111111094E-2</v>
       </c>
       <c r="I71" s="30">
-        <v>0.54166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J71" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.73402777777777772</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C72" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D72" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D72" s="27"/>
       <c r="E72" s="27" t="s">
         <v>62</v>
       </c>
@@ -5663,17 +5544,17 @@
         <v>15</v>
       </c>
       <c r="G72" s="28" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H72" s="29">
         <f t="shared" si="1"/>
-        <v>6.7361111111111094E-2</v>
+        <v>3.2638888888888884E-2</v>
       </c>
       <c r="I72" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J72" s="30">
-        <v>0.73402777777777772</v>
+        <v>0.3659722222222222</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5686,30 +5567,28 @@
       <c r="C73" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D73" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D73" s="27"/>
       <c r="E73" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F73" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G73" s="28" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="H73" s="29">
         <f t="shared" si="1"/>
-        <v>3.2638888888888884E-2</v>
+        <v>9.2361111111111116E-2</v>
       </c>
       <c r="I73" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.3659722222222222</v>
       </c>
       <c r="J73" s="30">
-        <v>0.3659722222222222</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A74" s="22">
         <v>46129</v>
       </c>
@@ -5719,30 +5598,28 @@
       <c r="C74" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D74" s="27"/>
       <c r="E74" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F74" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G74" s="28" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H74" s="29">
         <f t="shared" si="1"/>
-        <v>9.2361111111111116E-2</v>
+        <v>4.1666666666666685E-2</v>
       </c>
       <c r="I74" s="30">
-        <v>0.3659722222222222</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J74" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A75" s="22">
         <v>46129</v>
       </c>
@@ -5752,27 +5629,25 @@
       <c r="C75" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D75" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D75" s="27"/>
       <c r="E75" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F75" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G75" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H75" s="29">
         <f t="shared" si="1"/>
-        <v>4.1666666666666685E-2</v>
+        <v>0.125</v>
       </c>
       <c r="I75" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J75" s="30">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5785,68 +5660,52 @@
       <c r="C76" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D76" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D76" s="27"/>
       <c r="E76" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F76" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G76" s="28" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H76" s="29">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>2.430555555555558E-2</v>
       </c>
       <c r="I76" s="30">
-        <v>0.54166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J76" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
-      <c r="A77" s="22">
-        <v>46129</v>
-      </c>
-      <c r="B77" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D77" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="E77" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F77" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="H77" s="29">
-        <f t="shared" si="1"/>
-        <v>2.430555555555558E-2</v>
-      </c>
-      <c r="I77" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J77" s="30">
         <v>0.69097222222222221</v>
       </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A77" s="31">
+        <v>46130</v>
+      </c>
+      <c r="B77" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="32"/>
+      <c r="F77" s="32"/>
+      <c r="G77" s="33"/>
+      <c r="H77" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I77" s="35"/>
+      <c r="J77" s="35"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="31">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C78" s="32"/>
       <c r="D78" s="32"/>
@@ -5860,24 +5719,36 @@
       <c r="I78" s="35"/>
       <c r="J78" s="35"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A79" s="31">
-        <v>46131</v>
-      </c>
-      <c r="B79" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="33"/>
-      <c r="H79" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="35"/>
-      <c r="J79" s="35"/>
+    <row r="79" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+      <c r="A79" s="22">
+        <v>46132</v>
+      </c>
+      <c r="B79" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F79" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="H79" s="29">
+        <f t="shared" si="1"/>
+        <v>4.8611111111111494E-3</v>
+      </c>
+      <c r="I79" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J79" s="30">
+        <v>0.33819444444444446</v>
+      </c>
     </row>
     <row r="80" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A80" s="22">
@@ -5889,27 +5760,25 @@
       <c r="C80" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D80" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D80" s="27"/>
       <c r="E80" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F80" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G80" s="28" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H80" s="29">
         <f t="shared" si="1"/>
-        <v>4.8611111111111494E-3</v>
+        <v>0.12013888888888885</v>
       </c>
       <c r="I80" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.33819444444444446</v>
       </c>
       <c r="J80" s="30">
-        <v>0.33819444444444446</v>
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5922,27 +5791,25 @@
       <c r="C81" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D81" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D81" s="27"/>
       <c r="E81" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F81" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G81" s="28" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="H81" s="29">
         <f t="shared" si="1"/>
-        <v>0.12013888888888885</v>
+        <v>2.7777777777778234E-3</v>
       </c>
       <c r="I81" s="30">
-        <v>0.33819444444444446</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J81" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.46111111111111114</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -5955,30 +5822,28 @@
       <c r="C82" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D82" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D82" s="27"/>
       <c r="E82" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F82" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G82" s="28" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="H82" s="29">
         <f t="shared" si="1"/>
-        <v>2.7777777777778234E-3</v>
+        <v>4.2361111111111072E-2</v>
       </c>
       <c r="I82" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.46111111111111114</v>
       </c>
       <c r="J82" s="30">
-        <v>0.46111111111111114</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.50347222222222221</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A83" s="22">
         <v>46132</v>
       </c>
@@ -5988,27 +5853,25 @@
       <c r="C83" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D83" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D83" s="27"/>
       <c r="E83" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F83" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G83" s="28" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="H83" s="29">
         <f t="shared" si="1"/>
-        <v>4.2361111111111072E-2</v>
+        <v>0.125</v>
       </c>
       <c r="I83" s="30">
-        <v>0.46111111111111114</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J83" s="30">
-        <v>0.50347222222222221</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
@@ -6021,9 +5884,7 @@
       <c r="C84" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D84" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D84" s="27"/>
       <c r="E84" s="27" t="s">
         <v>62</v>
       </c>
@@ -6031,32 +5892,30 @@
         <v>15</v>
       </c>
       <c r="G84" s="28" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H84" s="29">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>5.0694444444444486E-2</v>
       </c>
       <c r="I84" s="30">
-        <v>0.54166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J84" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.71736111111111112</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A85" s="22">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C85" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D85" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D85" s="27"/>
       <c r="E85" s="27" t="s">
         <v>62</v>
       </c>
@@ -6064,17 +5923,17 @@
         <v>15</v>
       </c>
       <c r="G85" s="28" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="H85" s="29">
         <f t="shared" si="1"/>
-        <v>5.0694444444444486E-2</v>
+        <v>5.5555555555555913E-3</v>
       </c>
       <c r="I85" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J85" s="30">
-        <v>0.71736111111111112</v>
+        <v>0.33888888888888891</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -6087,30 +5946,28 @@
       <c r="C86" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D86" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D86" s="27"/>
       <c r="E86" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F86" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G86" s="28" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H86" s="29">
         <f t="shared" si="1"/>
-        <v>5.5555555555555913E-3</v>
+        <v>0.11944444444444441</v>
       </c>
       <c r="I86" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.33888888888888891</v>
       </c>
       <c r="J86" s="30">
-        <v>0.33888888888888891</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A87" s="22">
         <v>46133</v>
       </c>
@@ -6120,30 +5977,28 @@
       <c r="C87" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D87" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D87" s="27"/>
       <c r="E87" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F87" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G87" s="28" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="H87" s="29">
         <f t="shared" si="1"/>
-        <v>0.11944444444444441</v>
+        <v>3.9583333333333359E-2</v>
       </c>
       <c r="I87" s="30">
-        <v>0.33888888888888891</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J87" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.49791666666666667</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A88" s="22">
         <v>46133</v>
       </c>
@@ -6153,30 +6008,28 @@
       <c r="C88" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D88" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D88" s="27"/>
       <c r="E88" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F88" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G88" s="28" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="H88" s="29">
         <f t="shared" si="1"/>
-        <v>3.9583333333333359E-2</v>
+        <v>0.125</v>
       </c>
       <c r="I88" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J88" s="30">
-        <v>0.49791666666666667</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A89" s="22">
         <v>46133</v>
       </c>
@@ -6186,42 +6039,38 @@
       <c r="C89" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D89" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D89" s="27"/>
       <c r="E89" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F89" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G89" s="28" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="H89" s="29">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>4.5138888888888951E-2</v>
       </c>
       <c r="I89" s="30">
-        <v>0.54166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J89" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.71180555555555558</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A90" s="22">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B90" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C90" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D90" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D90" s="27"/>
       <c r="E90" s="27" t="s">
         <v>62</v>
       </c>
@@ -6229,20 +6078,20 @@
         <v>15</v>
       </c>
       <c r="G90" s="28" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="H90" s="29">
         <f t="shared" si="1"/>
-        <v>4.5138888888888951E-2</v>
+        <v>2.7777777777778234E-3</v>
       </c>
       <c r="I90" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J90" s="30">
-        <v>0.71180555555555558</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.33611111111111114</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="22">
         <v>46134</v>
       </c>
@@ -6252,27 +6101,25 @@
       <c r="C91" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D91" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D91" s="27"/>
       <c r="E91" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F91" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G91" s="28" t="s">
-        <v>221</v>
+      <c r="G91" s="27" t="s">
+        <v>230</v>
       </c>
       <c r="H91" s="29">
         <f t="shared" si="1"/>
-        <v>2.7777777777778234E-3</v>
+        <v>0.12222222222222218</v>
       </c>
       <c r="I91" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.33611111111111114</v>
       </c>
       <c r="J91" s="30">
-        <v>0.33611111111111114</v>
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
@@ -6285,27 +6132,25 @@
       <c r="C92" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D92" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D92" s="27"/>
       <c r="E92" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F92" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G92" s="27" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="H92" s="29">
         <f t="shared" si="1"/>
-        <v>0.12222222222222218</v>
+        <v>5.2083333333333315E-2</v>
       </c>
       <c r="I92" s="30">
-        <v>0.33611111111111114</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J92" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.51041666666666663</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
@@ -6318,27 +6163,25 @@
       <c r="C93" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D93" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D93" s="27"/>
       <c r="E93" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F93" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G93" s="27" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="H93" s="29">
         <f t="shared" si="1"/>
-        <v>5.2083333333333315E-2</v>
+        <v>0.10416666666666663</v>
       </c>
       <c r="I93" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.5625</v>
       </c>
       <c r="J93" s="30">
-        <v>0.51041666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
@@ -6351,60 +6194,56 @@
       <c r="C94" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D94" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D94" s="27"/>
       <c r="E94" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F94" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G94" s="27" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="H94" s="29">
         <f t="shared" si="1"/>
-        <v>0.10416666666666663</v>
+        <v>4.861111111111116E-2</v>
       </c>
       <c r="I94" s="30">
-        <v>0.5625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J94" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.71527777777777779</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A95" s="22">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C95" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D95" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D95" s="27"/>
       <c r="E95" s="27" t="s">
         <v>62</v>
       </c>
       <c r="F95" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G95" s="27" t="s">
-        <v>245</v>
+      <c r="G95" s="28" t="s">
+        <v>221</v>
       </c>
       <c r="H95" s="29">
         <f t="shared" si="1"/>
-        <v>4.861111111111116E-2</v>
+        <v>2.7777777777778234E-3</v>
       </c>
       <c r="I95" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J95" s="30">
-        <v>0.71527777777777779</v>
+        <v>0.33611111111111114</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -6417,30 +6256,28 @@
       <c r="C96" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D96" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D96" s="27"/>
       <c r="E96" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F96" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G96" s="28" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H96" s="29">
         <f t="shared" si="1"/>
-        <v>2.7777777777778234E-3</v>
+        <v>0.12222222222222218</v>
       </c>
       <c r="I96" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.33611111111111114</v>
       </c>
       <c r="J96" s="30">
-        <v>0.33611111111111114</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A97" s="22">
         <v>46135</v>
       </c>
@@ -6450,30 +6287,28 @@
       <c r="C97" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D97" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D97" s="27"/>
       <c r="E97" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F97" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G97" s="28" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="H97" s="29">
         <f t="shared" si="1"/>
-        <v>0.12222222222222218</v>
+        <v>4.9305555555555547E-2</v>
       </c>
       <c r="I97" s="30">
-        <v>0.33611111111111114</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J97" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.50763888888888886</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A98" s="22">
         <v>46135</v>
       </c>
@@ -6483,30 +6318,28 @@
       <c r="C98" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D98" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D98" s="27"/>
       <c r="E98" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F98" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G98" s="28" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="H98" s="29">
         <f t="shared" si="1"/>
-        <v>4.9305555555555547E-2</v>
+        <v>0.10069444444444442</v>
       </c>
       <c r="I98" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.56597222222222221</v>
       </c>
       <c r="J98" s="30">
-        <v>0.50763888888888886</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A99" s="22">
         <v>46135</v>
       </c>
@@ -6516,9 +6349,7 @@
       <c r="C99" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D99" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D99" s="27"/>
       <c r="E99" s="27" t="s">
         <v>33</v>
       </c>
@@ -6526,65 +6357,61 @@
         <v>15</v>
       </c>
       <c r="G99" s="28" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="H99" s="29">
         <f t="shared" si="1"/>
-        <v>0.10069444444444442</v>
+        <v>3.6805555555555647E-2</v>
       </c>
       <c r="I99" s="30">
-        <v>0.56597222222222221</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J99" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.70347222222222228</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A100" s="22">
         <v>46135</v>
       </c>
       <c r="B100" s="22" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="C100" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D100" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D100" s="27"/>
       <c r="E100" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F100" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G100" s="28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H100" s="29">
         <f t="shared" si="1"/>
-        <v>3.6805555555555647E-2</v>
+        <v>3.125E-2</v>
       </c>
       <c r="I100" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.70347222222222228</v>
       </c>
       <c r="J100" s="30">
-        <v>0.70347222222222228</v>
+        <v>0.73472222222222228</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A101" s="22">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B101" s="22" t="s">
-        <v>246</v>
+        <v>11</v>
       </c>
       <c r="C101" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D101" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D101" s="27"/>
       <c r="E101" s="27" t="s">
         <v>62</v>
       </c>
@@ -6592,17 +6419,17 @@
         <v>15</v>
       </c>
       <c r="G101" s="28" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="H101" s="29">
         <f t="shared" si="1"/>
-        <v>3.125E-2</v>
+        <v>9.0277777777778012E-3</v>
       </c>
       <c r="I101" s="30">
-        <v>0.70347222222222228</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J101" s="30">
-        <v>0.73472222222222228</v>
+        <v>0.34236111111111112</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -6615,30 +6442,28 @@
       <c r="C102" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D102" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D102" s="27"/>
       <c r="E102" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F102" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G102" s="28" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H102" s="29">
         <f t="shared" si="1"/>
-        <v>9.0277777777778012E-3</v>
+        <v>0.1159722222222222</v>
       </c>
       <c r="I102" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.34236111111111112</v>
       </c>
       <c r="J102" s="30">
-        <v>0.34236111111111112</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A103" s="22">
         <v>46136</v>
       </c>
@@ -6648,30 +6473,28 @@
       <c r="C103" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D103" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D103" s="27"/>
       <c r="E103" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F103" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G103" s="28" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="H103" s="29">
         <f t="shared" si="1"/>
-        <v>0.1159722222222222</v>
+        <v>3.4027777777777823E-2</v>
       </c>
       <c r="I103" s="30">
-        <v>0.34236111111111112</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J103" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.49236111111111114</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A104" s="22">
         <v>46136</v>
       </c>
@@ -6681,27 +6504,25 @@
       <c r="C104" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D104" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D104" s="27"/>
       <c r="E104" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F104" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G104" s="28" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="H104" s="29">
         <f t="shared" si="1"/>
-        <v>3.4027777777777823E-2</v>
+        <v>2.8472222222222232E-2</v>
       </c>
       <c r="I104" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.49236111111111114</v>
       </c>
       <c r="J104" s="30">
-        <v>0.49236111111111114</v>
+        <v>0.52083333333333337</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -6714,9 +6535,7 @@
       <c r="C105" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D105" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D105" s="27"/>
       <c r="E105" s="27" t="s">
         <v>33</v>
       </c>
@@ -6728,16 +6547,16 @@
       </c>
       <c r="H105" s="29">
         <f t="shared" si="1"/>
-        <v>2.8472222222222232E-2</v>
+        <v>4.0972222222222188E-2</v>
       </c>
       <c r="I105" s="30">
-        <v>0.49236111111111114</v>
+        <v>0.56319444444444444</v>
       </c>
       <c r="J105" s="30">
-        <v>0.52083333333333337</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A106" s="22">
         <v>46136</v>
       </c>
@@ -6747,30 +6566,28 @@
       <c r="C106" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D106" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D106" s="27"/>
       <c r="E106" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F106" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G106" s="28" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="H106" s="29">
         <f t="shared" si="1"/>
-        <v>4.0972222222222188E-2</v>
+        <v>5.5555555555556468E-3</v>
       </c>
       <c r="I106" s="30">
-        <v>0.56319444444444444</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="J106" s="30">
-        <v>0.60416666666666663</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.60972222222222228</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A107" s="22">
         <v>46136</v>
       </c>
@@ -6780,27 +6597,25 @@
       <c r="C107" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D107" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D107" s="27"/>
       <c r="E107" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F107" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G107" s="28" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H107" s="29">
         <f t="shared" si="1"/>
-        <v>5.5555555555556468E-3</v>
+        <v>5.6944444444444353E-2</v>
       </c>
       <c r="I107" s="30">
-        <v>0.60416666666666663</v>
+        <v>0.60972222222222228</v>
       </c>
       <c r="J107" s="30">
-        <v>0.60972222222222228</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -6813,68 +6628,52 @@
       <c r="C108" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D108" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D108" s="27"/>
       <c r="E108" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F108" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G108" s="28" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H108" s="29">
         <f t="shared" si="1"/>
-        <v>5.6944444444444353E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I108" s="30">
-        <v>0.60972222222222228</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J108" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
-      <c r="A109" s="22">
-        <v>46136</v>
-      </c>
-      <c r="B109" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C109" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D109" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="E109" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F109" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G109" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="H109" s="29">
-        <f t="shared" si="1"/>
-        <v>6.25E-2</v>
-      </c>
-      <c r="I109" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J109" s="30">
         <v>0.72916666666666663</v>
       </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A109" s="31">
+        <v>46137</v>
+      </c>
+      <c r="B109" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109" s="32"/>
+      <c r="D109" s="32"/>
+      <c r="E109" s="32"/>
+      <c r="F109" s="32"/>
+      <c r="G109" s="33"/>
+      <c r="H109" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I109" s="35"/>
+      <c r="J109" s="35"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="31">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C110" s="32"/>
       <c r="D110" s="32"/>
@@ -6889,56 +6688,68 @@
       <c r="J110" s="35"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A111" s="31">
-        <v>46138</v>
-      </c>
-      <c r="B111" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" s="32"/>
-      <c r="D111" s="32"/>
-      <c r="E111" s="32"/>
-      <c r="F111" s="32"/>
-      <c r="G111" s="33"/>
-      <c r="H111" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I111" s="35"/>
-      <c r="J111" s="35"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A112" s="47">
+      <c r="A111" s="47">
         <v>46139</v>
       </c>
-      <c r="B112" s="47" t="s">
+      <c r="B111" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="48" t="s">
+      <c r="C111" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="D112" s="48"/>
-      <c r="E112" s="48" t="s">
+      <c r="D111" s="48"/>
+      <c r="E111" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="F112" s="48" t="s">
+      <c r="F111" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="G112" s="49" t="s">
+      <c r="G111" s="49" t="s">
         <v>179</v>
       </c>
-      <c r="H112" s="50">
+      <c r="H111" s="50">
         <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="I112" s="51">
+      <c r="I111" s="51">
         <v>0.33333333333333331</v>
       </c>
-      <c r="J112" s="51">
+      <c r="J111" s="51">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+      <c r="A112" s="22">
+        <v>46140</v>
+      </c>
+      <c r="B112" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C112" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D112" s="27"/>
+      <c r="E112" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F112" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G112" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="H112" s="29">
+        <f t="shared" si="1"/>
+        <v>4.1666666666667074E-3</v>
+      </c>
+      <c r="I112" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J112" s="30">
+        <v>0.33750000000000002</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A113" s="22">
         <v>46140</v>
       </c>
@@ -6948,27 +6759,25 @@
       <c r="C113" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D113" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D113" s="27"/>
       <c r="E113" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F113" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G113" s="28" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H113" s="29">
         <f t="shared" si="1"/>
-        <v>4.1666666666667074E-3</v>
+        <v>0.125</v>
       </c>
       <c r="I113" s="30">
         <v>0.33333333333333331</v>
       </c>
       <c r="J113" s="30">
-        <v>0.33750000000000002</v>
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
@@ -6981,27 +6790,25 @@
       <c r="C114" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D114" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D114" s="27"/>
       <c r="E114" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F114" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G114" s="28" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="H114" s="29">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>4.3055555555555569E-2</v>
       </c>
       <c r="I114" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J114" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.50138888888888888</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
@@ -7014,27 +6821,25 @@
       <c r="C115" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D115" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D115" s="27"/>
       <c r="E115" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F115" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G115" s="28" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="H115" s="29">
         <f t="shared" si="1"/>
-        <v>4.3055555555555569E-2</v>
+        <v>5.902777777777779E-2</v>
       </c>
       <c r="I115" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.54513888888888884</v>
       </c>
       <c r="J115" s="30">
-        <v>0.50138888888888888</v>
+        <v>0.60416666666666663</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
@@ -7047,27 +6852,25 @@
       <c r="C116" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D116" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D116" s="27"/>
       <c r="E116" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F116" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G116" s="28" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H116" s="29">
         <f t="shared" si="1"/>
-        <v>5.902777777777779E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I116" s="30">
-        <v>0.54513888888888884</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="J116" s="30">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
@@ -7080,9 +6883,7 @@
       <c r="C117" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D117" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D117" s="27"/>
       <c r="E117" s="27" t="s">
         <v>62</v>
       </c>
@@ -7090,32 +6891,30 @@
         <v>15</v>
       </c>
       <c r="G117" s="28" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H117" s="29">
         <f t="shared" si="1"/>
-        <v>6.25E-2</v>
+        <v>4.5138888888888951E-2</v>
       </c>
       <c r="I117" s="30">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J117" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.71180555555555558</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A118" s="22">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B118" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C118" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D118" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D118" s="27"/>
       <c r="E118" s="27" t="s">
         <v>62</v>
       </c>
@@ -7123,17 +6922,17 @@
         <v>15</v>
       </c>
       <c r="G118" s="28" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="H118" s="29">
         <f t="shared" si="1"/>
-        <v>4.5138888888888951E-2</v>
+        <v>1.3194444444444453E-2</v>
       </c>
       <c r="I118" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J118" s="30">
-        <v>0.71180555555555558</v>
+        <v>0.34652777777777777</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -7146,30 +6945,28 @@
       <c r="C119" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D119" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D119" s="27"/>
       <c r="E119" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F119" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G119" s="28" t="s">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="H119" s="29">
         <f t="shared" si="1"/>
-        <v>1.3194444444444453E-2</v>
+        <v>4.9305555555555547E-2</v>
       </c>
       <c r="I119" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.34652777777777777</v>
       </c>
       <c r="J119" s="30">
-        <v>0.34652777777777777</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.39583333333333331</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A120" s="22">
         <v>46141</v>
       </c>
@@ -7179,30 +6976,28 @@
       <c r="C120" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D120" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D120" s="27"/>
       <c r="E120" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F120" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G120" s="28" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="H120" s="29">
         <f t="shared" si="1"/>
-        <v>4.9305555555555547E-2</v>
+        <v>5.7638888888888906E-2</v>
       </c>
       <c r="I120" s="30">
-        <v>0.34652777777777777</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="J120" s="30">
-        <v>0.39583333333333331</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.45347222222222222</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A121" s="22">
         <v>46141</v>
       </c>
@@ -7212,9 +7007,7 @@
       <c r="C121" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D121" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D121" s="27"/>
       <c r="E121" s="27" t="s">
         <v>62</v>
       </c>
@@ -7222,17 +7015,17 @@
         <v>15</v>
       </c>
       <c r="G121" s="28" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H121" s="29">
         <f t="shared" si="1"/>
-        <v>5.7638888888888906E-2</v>
+        <v>3.3333333333333326E-2</v>
       </c>
       <c r="I121" s="30">
-        <v>0.39583333333333331</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J121" s="30">
-        <v>0.45347222222222222</v>
+        <v>0.49166666666666664</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -7245,27 +7038,25 @@
       <c r="C122" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D122" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D122" s="27"/>
       <c r="E122" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F122" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G122" s="28" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H122" s="29">
         <f t="shared" si="1"/>
-        <v>3.3333333333333326E-2</v>
+        <v>2.916666666666673E-2</v>
       </c>
       <c r="I122" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.49166666666666664</v>
       </c>
       <c r="J122" s="30">
-        <v>0.49166666666666664</v>
+        <v>0.52083333333333337</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -7278,9 +7069,7 @@
       <c r="C123" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D123" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D123" s="27"/>
       <c r="E123" s="27" t="s">
         <v>33</v>
       </c>
@@ -7288,20 +7077,20 @@
         <v>15</v>
       </c>
       <c r="G123" s="28" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H123" s="29">
         <f t="shared" si="1"/>
-        <v>2.916666666666673E-2</v>
+        <v>0.10416666666666663</v>
       </c>
       <c r="I123" s="30">
-        <v>0.49166666666666664</v>
+        <v>0.5625</v>
       </c>
       <c r="J123" s="30">
-        <v>0.52083333333333337</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A124" s="22">
         <v>46141</v>
       </c>
@@ -7311,42 +7100,38 @@
       <c r="C124" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D124" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D124" s="27"/>
       <c r="E124" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F124" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G124" s="28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H124" s="29">
         <f t="shared" si="1"/>
-        <v>0.10416666666666663</v>
+        <v>4.5138888888888951E-2</v>
       </c>
       <c r="I124" s="30">
-        <v>0.5625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J124" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.71180555555555558</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A125" s="22">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B125" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C125" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D125" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D125" s="27"/>
       <c r="E125" s="27" t="s">
         <v>62</v>
       </c>
@@ -7354,17 +7139,17 @@
         <v>15</v>
       </c>
       <c r="G125" s="28" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="H125" s="29">
         <f t="shared" si="1"/>
-        <v>4.5138888888888951E-2</v>
+        <v>1.4583333333333337E-2</v>
       </c>
       <c r="I125" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J125" s="30">
-        <v>0.71180555555555558</v>
+        <v>0.34791666666666665</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -7377,30 +7162,28 @@
       <c r="C126" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D126" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D126" s="27"/>
       <c r="E126" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F126" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G126" s="28" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="H126" s="29">
         <f t="shared" si="1"/>
-        <v>1.4583333333333337E-2</v>
+        <v>6.8750000000000033E-2</v>
       </c>
       <c r="I126" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.34791666666666665</v>
       </c>
       <c r="J126" s="30">
-        <v>0.34791666666666665</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A127" s="22">
         <v>46142</v>
       </c>
@@ -7410,30 +7193,28 @@
       <c r="C127" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D127" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D127" s="27"/>
       <c r="E127" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F127" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G127" s="28" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H127" s="29">
         <f t="shared" si="1"/>
-        <v>6.8750000000000033E-2</v>
+        <v>4.2361111111111072E-2</v>
       </c>
       <c r="I127" s="30">
-        <v>0.34791666666666665</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J127" s="30">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.45902777777777776</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A128" s="22">
         <v>46142</v>
       </c>
@@ -7443,27 +7224,25 @@
       <c r="C128" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D128" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D128" s="27"/>
       <c r="E128" s="27" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F128" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G128" s="28" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H128" s="29">
         <f t="shared" si="1"/>
-        <v>4.2361111111111072E-2</v>
+        <v>6.1805555555555614E-2</v>
       </c>
       <c r="I128" s="30">
-        <v>0.41666666666666669</v>
+        <v>0.45902777777777776</v>
       </c>
       <c r="J128" s="30">
-        <v>0.45902777777777776</v>
+        <v>0.52083333333333337</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
@@ -7476,9 +7255,7 @@
       <c r="C129" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D129" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D129" s="27"/>
       <c r="E129" s="27" t="s">
         <v>33</v>
       </c>
@@ -7486,20 +7263,20 @@
         <v>15</v>
       </c>
       <c r="G129" s="28" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H129" s="29">
         <f t="shared" si="1"/>
-        <v>6.1805555555555614E-2</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="I129" s="30">
-        <v>0.45902777777777776</v>
+        <v>0.5625</v>
       </c>
       <c r="J129" s="30">
-        <v>0.52083333333333337</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A130" s="22">
         <v>46142</v>
       </c>
@@ -7509,30 +7286,28 @@
       <c r="C130" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D130" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D130" s="27"/>
       <c r="E130" s="27" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F130" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G130" s="28" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="H130" s="29">
         <f t="shared" si="1"/>
-        <v>4.166666666666663E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I130" s="30">
-        <v>0.5625</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="J130" s="30">
-        <v>0.60416666666666663</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="22">
         <v>46142</v>
       </c>
@@ -7542,9 +7317,7 @@
       <c r="C131" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D131" s="27" t="s">
-        <v>261</v>
-      </c>
+      <c r="D131" s="27"/>
       <c r="E131" s="27" t="s">
         <v>62</v>
       </c>
@@ -7552,139 +7325,115 @@
         <v>15</v>
       </c>
       <c r="G131" s="28" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="H131" s="29">
         <f t="shared" si="1"/>
-        <v>6.25E-2</v>
+        <v>4.9305555555555602E-2</v>
       </c>
       <c r="I131" s="30">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J131" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A132" s="22">
-        <v>46142</v>
-      </c>
-      <c r="B132" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C132" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D132" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="E132" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F132" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G132" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="H132" s="29">
-        <f t="shared" si="1"/>
-        <v>4.9305555555555602E-2</v>
-      </c>
-      <c r="I132" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J132" s="30">
         <v>0.71597222222222223</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="46"/>
-      <c r="B133" s="46"/>
-      <c r="G133" s="40"/>
-      <c r="H133" s="64"/>
-      <c r="I133" s="65"/>
-      <c r="J133" s="65"/>
-    </row>
-    <row r="134" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="46"/>
+      <c r="B132" s="46"/>
+      <c r="G132" s="40"/>
+      <c r="H132" s="64"/>
+      <c r="I132" s="65"/>
+      <c r="J132" s="65"/>
+    </row>
+    <row r="133" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="4"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="5"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F133" s="8">
+        <v>152</v>
+      </c>
+      <c r="H133" s="40"/>
+    </row>
+    <row r="134" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
-      <c r="C134" s="5"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F134" s="8">
-        <v>152</v>
+      <c r="C134" s="9"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F134" s="11">
+        <v>19</v>
       </c>
       <c r="H134" s="40"/>
     </row>
     <row r="135" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="4"/>
-      <c r="B135" s="4"/>
-      <c r="C135" s="9"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F135" s="11">
-        <v>19</v>
-      </c>
+      <c r="A135" s="125" t="s">
+        <v>23</v>
+      </c>
+      <c r="B135" s="125"/>
+      <c r="C135" s="125"/>
+      <c r="D135" s="12"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
       <c r="H135" s="40"/>
     </row>
-    <row r="136" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="125" t="s">
-        <v>23</v>
-      </c>
-      <c r="B136" s="125"/>
-      <c r="C136" s="125"/>
-      <c r="D136" s="12"/>
-      <c r="E136" s="2"/>
-      <c r="F136" s="2"/>
-      <c r="H136" s="40"/>
-    </row>
-    <row r="137" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A137" s="13"/>
-      <c r="B137" s="13"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="14" t="s">
+    <row r="136" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A136" s="13"/>
+      <c r="B136" s="13"/>
+      <c r="C136" s="6"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F137" s="15">
-        <f>SUMIF(F9:F132,"Billable",H9:H132)</f>
-        <v>0</v>
-      </c>
-      <c r="H137" s="38"/>
-    </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="126" t="s">
+      <c r="F136" s="15">
+        <f>SUMIF(F9:F131,"Billable",H9:H131)</f>
+        <v>0</v>
+      </c>
+      <c r="H136" s="38"/>
+    </row>
+    <row r="137" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="B138" s="126"/>
-      <c r="C138" s="126"/>
-      <c r="D138" s="16"/>
-      <c r="E138" s="17" t="s">
+      <c r="B137" s="126"/>
+      <c r="C137" s="126"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="F138" s="18">
-        <f>SUMIF(F9:F132,"Non-Billable",H9:H132)</f>
-        <v>7.6631944444444482</v>
+      <c r="F137" s="18">
+        <f>SUMIF(F9:F131,"Non-Billable",H9:H131)</f>
+        <v>7.6513888888888921</v>
+      </c>
+      <c r="H137" s="40"/>
+    </row>
+    <row r="138" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F138" s="44">
+        <f>F136+F137</f>
+        <v>7.6513888888888921</v>
       </c>
       <c r="H138" s="40"/>
     </row>
-    <row r="139" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
-      <c r="E139" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F139" s="44">
-        <f>F137+F138</f>
-        <v>7.6631944444444482</v>
-      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
       <c r="H139" s="40"/>
     </row>
     <row r="140" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -7692,29 +7441,20 @@
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
-      <c r="F140" s="2"/>
+      <c r="E140" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F140" s="21"/>
       <c r="H140" s="40"/>
     </row>
-    <row r="141" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="2"/>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F141" s="21"/>
+    <row r="141" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E141" s="39"/>
       <c r="H141" s="40"/>
-    </row>
-    <row r="142" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E142" s="39"/>
-      <c r="H142" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A136:C136"/>
-    <mergeCell ref="A138:C138"/>
+    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A137:C137"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D7:E7">
@@ -7740,7 +7480,7 @@
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:B142">
+  <conditionalFormatting sqref="B8:B141">
     <cfRule type="containsText" dxfId="88" priority="1" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B8)))</formula>
     </cfRule>
@@ -7748,31 +7488,31 @@
       <formula>NOT(ISERROR(SEARCH("Sunday",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D134:E134 D136:E138 E141">
+  <conditionalFormatting sqref="D133:E133 D135:E137 E140">
     <cfRule type="containsText" dxfId="86" priority="3" operator="containsText" text="Religious Leave">
-      <formula>NOT(ISERROR(SEARCH("Religious Leave",D134)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Religious Leave",D133)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="85" priority="4" operator="containsText" text="Birthday Leave">
-      <formula>NOT(ISERROR(SEARCH("Birthday Leave",D134)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Birthday Leave",D133)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="84" priority="5" operator="containsText" text="Study Leave">
-      <formula>NOT(ISERROR(SEARCH("Study Leave",D134)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Study Leave",D133)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="83" priority="6" operator="containsText" text="Family Responsibility Leave">
-      <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D134)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D133)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="82" priority="7" operator="containsText" text="Sick Leave">
-      <formula>NOT(ISERROR(SEARCH("Sick Leave",D134)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Sick Leave",D133)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="81" priority="8" operator="containsText" text="Annual Leave">
-      <formula>NOT(ISERROR(SEARCH("Annual Leave",D134)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Annual Leave",D133)))</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="80" priority="9" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="time" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Time Format" error="Please input a valid time. For e.g. 08:00" sqref="J59 I9:J58 I60:J133" xr:uid="{68437EC4-DD9C-463B-9F8D-7339DE1FDE4C}">
+    <dataValidation type="time" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Time Format" error="Please input a valid time. For e.g. 08:00" sqref="J58 I59:J132 I9:J57" xr:uid="{68437EC4-DD9C-463B-9F8D-7339DE1FDE4C}">
       <formula1>0</formula1>
       <formula2>0.999988425925926</formula2>
     </dataValidation>
@@ -7793,19 +7533,19 @@
           <x14:formula1>
             <xm:f>Key!$J$3:$J$4</xm:f>
           </x14:formula1>
-          <xm:sqref>F9:F133</xm:sqref>
+          <xm:sqref>F9:F132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D174978-0CE3-4483-935A-E2D2B6171911}">
           <x14:formula1>
             <xm:f>Key!$F$3:$F$47</xm:f>
           </x14:formula1>
-          <xm:sqref>E9:E133</xm:sqref>
+          <xm:sqref>E9:E132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2056345A-D817-415C-BFFF-52AAC88A616B}">
           <x14:formula1>
             <xm:f>Key!$B$2:$B$54</xm:f>
           </x14:formula1>
-          <xm:sqref>C9:C133</xm:sqref>
+          <xm:sqref>C9:C132</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
+++ b/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_JabulanePoulo_2026\Projects\Timesheet\Jabulane_Poulo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCBF873A-6E14-4CED-A777-18CDD3C75C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B76767F-34EA-4DCF-9E5B-F271BA29BF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -1929,13 +1929,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1951,21 +1966,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3629,7 +3629,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="27" t="s">
@@ -12162,27 +12162,27 @@
       <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="135" t="s">
+      <c r="A8" s="132" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="138" t="s">
+      <c r="B9" s="129" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="139"/>
-      <c r="D9" s="138" t="s">
+      <c r="C9" s="130"/>
+      <c r="D9" s="129" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="139"/>
+      <c r="E9" s="130"/>
       <c r="F9" s="83" t="s">
         <v>95</v>
       </c>
@@ -12191,103 +12191,103 @@
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="129" t="s">
+      <c r="B10" s="131" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129" t="s">
+      <c r="C10" s="131"/>
+      <c r="D10" s="131" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="129"/>
+      <c r="E10" s="131"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="136" t="s">
+      <c r="G10" s="127" t="s">
         <v>169</v>
       </c>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="137"/>
-      <c r="K10" s="137"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="137"/>
-      <c r="O10" s="137"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="127" t="s">
+      <c r="B11" s="133" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="128"/>
-      <c r="D11" s="129" t="s">
+      <c r="C11" s="134"/>
+      <c r="D11" s="131" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="129"/>
+      <c r="E11" s="131"/>
       <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="133" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="128"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
       <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="127"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="129"/>
-      <c r="E13" s="129"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
       <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="127"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="134"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
       <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="133"/>
-      <c r="C15" s="134"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
       <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="127"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="134"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
       <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="130" t="s">
+      <c r="A17" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="131"/>
-      <c r="C17" s="131"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="132"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="137"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -12303,16 +12303,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -12322,6 +12312,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -13336,6 +13336,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -13473,22 +13488,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D445429-43EF-4578-A593-6E166DDD94D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84037CEB-E5D3-4F40-B93D-B68754BA7EB6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13506,23 +13523,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D445429-43EF-4578-A593-6E166DDD94D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{5138fff4-6130-46cf-adb5-ec5d984d54d5}" enabled="1" method="Privileged" siteId="{174c7352-9c5c-4558-b848-be140b444e7d}" contentBits="2" removed="0"/>

--- a/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
+++ b/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_JabulanePoulo_2026\Projects\Timesheet\Jabulane_Poulo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B76767F-34EA-4DCF-9E5B-F271BA29BF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011C515B-409D-4984-9758-4B7B87186AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -1929,28 +1929,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1966,6 +1951,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3629,7 +3629,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="27" t="s">
@@ -12162,27 +12162,27 @@
       <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="132" t="s">
+      <c r="A8" s="135" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="129" t="s">
+      <c r="B9" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="130"/>
-      <c r="D9" s="129" t="s">
+      <c r="C9" s="139"/>
+      <c r="D9" s="138" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="130"/>
+      <c r="E9" s="139"/>
       <c r="F9" s="83" t="s">
         <v>95</v>
       </c>
@@ -12191,103 +12191,103 @@
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="131" t="s">
+      <c r="B10" s="129" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="131"/>
-      <c r="D10" s="131" t="s">
+      <c r="C10" s="129"/>
+      <c r="D10" s="129" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="131"/>
+      <c r="E10" s="129"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="127" t="s">
+      <c r="G10" s="136" t="s">
         <v>169</v>
       </c>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="128"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="137"/>
+      <c r="K10" s="137"/>
+      <c r="L10" s="137"/>
+      <c r="M10" s="137"/>
+      <c r="N10" s="137"/>
+      <c r="O10" s="137"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="133" t="s">
+      <c r="B11" s="127" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="134"/>
-      <c r="D11" s="131" t="s">
+      <c r="C11" s="128"/>
+      <c r="D11" s="129" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="131"/>
+      <c r="E11" s="129"/>
       <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="133" t="s">
+      <c r="B12" s="127" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="134"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
+      <c r="C12" s="128"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
       <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="133"/>
-      <c r="C13" s="134"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="128"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
       <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="133"/>
-      <c r="C14" s="134"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="131"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
       <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="129"/>
       <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
       <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="135" t="s">
+      <c r="A17" s="130" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="137"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="132"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -12303,6 +12303,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -12312,16 +12322,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -13336,21 +13336,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -13488,24 +13473,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D445429-43EF-4578-A593-6E166DDD94D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84037CEB-E5D3-4F40-B93D-B68754BA7EB6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13523,6 +13506,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D445429-43EF-4578-A593-6E166DDD94D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{5138fff4-6130-46cf-adb5-ec5d984d54d5}" enabled="1" method="Privileged" siteId="{174c7352-9c5c-4558-b848-be140b444e7d}" contentBits="2" removed="0"/>

--- a/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
+++ b/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_JabulanePoulo_2026\Projects\Timesheet\Jabulane_Poulo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011C515B-409D-4984-9758-4B7B87186AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E13CB4-2E81-4D6F-B0C0-4ABDCFB946FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -1929,13 +1929,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1951,21 +1966,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3629,7 +3629,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="27" t="s">
@@ -12162,27 +12162,27 @@
       <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="135" t="s">
+      <c r="A8" s="132" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="138" t="s">
+      <c r="B9" s="129" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="139"/>
-      <c r="D9" s="138" t="s">
+      <c r="C9" s="130"/>
+      <c r="D9" s="129" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="139"/>
+      <c r="E9" s="130"/>
       <c r="F9" s="83" t="s">
         <v>95</v>
       </c>
@@ -12191,103 +12191,103 @@
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="129" t="s">
+      <c r="B10" s="131" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129" t="s">
+      <c r="C10" s="131"/>
+      <c r="D10" s="131" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="129"/>
+      <c r="E10" s="131"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="136" t="s">
+      <c r="G10" s="127" t="s">
         <v>169</v>
       </c>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="137"/>
-      <c r="K10" s="137"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="137"/>
-      <c r="O10" s="137"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="127" t="s">
+      <c r="B11" s="133" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="128"/>
-      <c r="D11" s="129" t="s">
+      <c r="C11" s="134"/>
+      <c r="D11" s="131" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="129"/>
+      <c r="E11" s="131"/>
       <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="133" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="128"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
       <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="127"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="129"/>
-      <c r="E13" s="129"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
       <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="127"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="134"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
       <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="133"/>
-      <c r="C15" s="134"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
       <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="127"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="134"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
       <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="130" t="s">
+      <c r="A17" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="131"/>
-      <c r="C17" s="131"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="132"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="137"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -12303,16 +12303,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -12322,6 +12312,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -13336,6 +13336,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -13473,22 +13488,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D445429-43EF-4578-A593-6E166DDD94D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84037CEB-E5D3-4F40-B93D-B68754BA7EB6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13506,23 +13523,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D445429-43EF-4578-A593-6E166DDD94D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{5138fff4-6130-46cf-adb5-ec5d984d54d5}" enabled="1" method="Privileged" siteId="{174c7352-9c5c-4558-b848-be140b444e7d}" contentBits="2" removed="0"/>

--- a/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
+++ b/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_JabulanePoulo_2026\Projects\Timesheet\Jabulane_Poulo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E13CB4-2E81-4D6F-B0C0-4ABDCFB946FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861FF522-721F-45D4-956B-0230E4B75EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -1929,28 +1929,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1966,6 +1951,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3629,7 +3629,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="27" t="s">
@@ -12162,27 +12162,27 @@
       <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="132" t="s">
+      <c r="A8" s="135" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="129" t="s">
+      <c r="B9" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="130"/>
-      <c r="D9" s="129" t="s">
+      <c r="C9" s="139"/>
+      <c r="D9" s="138" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="130"/>
+      <c r="E9" s="139"/>
       <c r="F9" s="83" t="s">
         <v>95</v>
       </c>
@@ -12191,103 +12191,103 @@
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="131" t="s">
+      <c r="B10" s="129" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="131"/>
-      <c r="D10" s="131" t="s">
+      <c r="C10" s="129"/>
+      <c r="D10" s="129" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="131"/>
+      <c r="E10" s="129"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="127" t="s">
+      <c r="G10" s="136" t="s">
         <v>169</v>
       </c>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="128"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="137"/>
+      <c r="K10" s="137"/>
+      <c r="L10" s="137"/>
+      <c r="M10" s="137"/>
+      <c r="N10" s="137"/>
+      <c r="O10" s="137"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="133" t="s">
+      <c r="B11" s="127" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="134"/>
-      <c r="D11" s="131" t="s">
+      <c r="C11" s="128"/>
+      <c r="D11" s="129" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="131"/>
+      <c r="E11" s="129"/>
       <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="133" t="s">
+      <c r="B12" s="127" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="134"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
+      <c r="C12" s="128"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
       <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="133"/>
-      <c r="C13" s="134"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="128"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
       <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="133"/>
-      <c r="C14" s="134"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="131"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
       <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="129"/>
       <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
       <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="135" t="s">
+      <c r="A17" s="130" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="137"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="132"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -12303,6 +12303,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -12312,16 +12322,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -13336,21 +13336,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -13488,24 +13473,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D445429-43EF-4578-A593-6E166DDD94D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84037CEB-E5D3-4F40-B93D-B68754BA7EB6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13523,6 +13506,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D445429-43EF-4578-A593-6E166DDD94D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{5138fff4-6130-46cf-adb5-ec5d984d54d5}" enabled="1" method="Privileged" siteId="{174c7352-9c5c-4558-b848-be140b444e7d}" contentBits="2" removed="0"/>

--- a/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
+++ b/Projects/Timesheet/Jabulane_Poulo/Jabulane_Poulo_April_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_JabulanePoulo_2026\Projects\Timesheet\Jabulane_Poulo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861FF522-721F-45D4-956B-0230E4B75EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F526583-37F7-427C-925F-5B6A6BBDE374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -1929,13 +1929,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1951,21 +1966,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3629,7 +3629,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="27" t="s">
@@ -12162,27 +12162,27 @@
       <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="135" t="s">
+      <c r="A8" s="132" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="138" t="s">
+      <c r="B9" s="129" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="139"/>
-      <c r="D9" s="138" t="s">
+      <c r="C9" s="130"/>
+      <c r="D9" s="129" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="139"/>
+      <c r="E9" s="130"/>
       <c r="F9" s="83" t="s">
         <v>95</v>
       </c>
@@ -12191,103 +12191,103 @@
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="129" t="s">
+      <c r="B10" s="131" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129" t="s">
+      <c r="C10" s="131"/>
+      <c r="D10" s="131" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="129"/>
+      <c r="E10" s="131"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="136" t="s">
+      <c r="G10" s="127" t="s">
         <v>169</v>
       </c>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="137"/>
-      <c r="K10" s="137"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="137"/>
-      <c r="O10" s="137"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="127" t="s">
+      <c r="B11" s="133" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="128"/>
-      <c r="D11" s="129" t="s">
+      <c r="C11" s="134"/>
+      <c r="D11" s="131" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="129"/>
+      <c r="E11" s="131"/>
       <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="133" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="128"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
       <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="127"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="129"/>
-      <c r="E13" s="129"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
       <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="127"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="134"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
       <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="133"/>
-      <c r="C15" s="134"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
       <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="127"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="134"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
       <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="130" t="s">
+      <c r="A17" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="131"/>
-      <c r="C17" s="131"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="132"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="137"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -12303,16 +12303,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -12322,6 +12312,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -13336,6 +13336,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -13473,22 +13488,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D445429-43EF-4578-A593-6E166DDD94D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84037CEB-E5D3-4F40-B93D-B68754BA7EB6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13506,23 +13523,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D445429-43EF-4578-A593-6E166DDD94D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{5138fff4-6130-46cf-adb5-ec5d984d54d5}" enabled="1" method="Privileged" siteId="{174c7352-9c5c-4558-b848-be140b444e7d}" contentBits="2" removed="0"/>
